--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BEE72E-27B9-0B48-AFC0-92A191D0F53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD08988-0C2A-2247-A470-5393F83E005E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>Donald Onana</t>
+  </si>
+  <si>
+    <t>Antoine Leberre</t>
+  </si>
+  <si>
+    <t>Braddy</t>
   </si>
 </sst>
 </file>
@@ -166,678 +172,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="70">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1167,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -1195,6 +530,9 @@
       <c r="B2" s="1">
         <v>46216</v>
       </c>
+      <c r="C2">
+        <v>79.599999999999994</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1203,6 +541,9 @@
       <c r="B3" s="1">
         <v>46216</v>
       </c>
+      <c r="C3">
+        <v>90.3</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1211,6 +552,9 @@
       <c r="B4" s="1">
         <v>46216</v>
       </c>
+      <c r="C4">
+        <v>81.8</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1241,6 +585,9 @@
       <c r="B7" s="1">
         <v>46216</v>
       </c>
+      <c r="C7">
+        <v>78.599999999999994</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1315,6 +662,9 @@
       <c r="B14" s="1">
         <v>46216</v>
       </c>
+      <c r="C14">
+        <v>64.900000000000006</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1323,6 +673,9 @@
       <c r="B15" s="1">
         <v>46216</v>
       </c>
+      <c r="C15">
+        <v>78.2</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1331,6 +684,9 @@
       <c r="B16" s="1">
         <v>46216</v>
       </c>
+      <c r="C16">
+        <v>61.2</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -1350,6 +706,9 @@
       <c r="B18" s="1">
         <v>46216</v>
       </c>
+      <c r="C18">
+        <v>69.5</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
@@ -1358,6 +717,9 @@
       <c r="B19" s="1">
         <v>46216</v>
       </c>
+      <c r="C19">
+        <v>78</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
@@ -1374,6 +736,9 @@
       <c r="B21" s="1">
         <v>46216</v>
       </c>
+      <c r="C21">
+        <v>66.400000000000006</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -1382,6 +747,9 @@
       <c r="B22" s="1">
         <v>46216</v>
       </c>
+      <c r="C22">
+        <v>61.5</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -1390,6 +758,9 @@
       <c r="B23" s="1">
         <v>46216</v>
       </c>
+      <c r="C23">
+        <v>67.900000000000006</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -1398,6 +769,9 @@
       <c r="B24" s="1">
         <v>46216</v>
       </c>
+      <c r="C24">
+        <v>67.900000000000006</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -1413,6 +787,28 @@
       </c>
       <c r="B26" s="1">
         <v>46216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46216</v>
+      </c>
+      <c r="C27">
+        <v>78.099999999999994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46216</v>
+      </c>
+      <c r="C28">
+        <v>56.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD08988-0C2A-2247-A470-5393F83E005E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDAE39-36AE-E045-8093-E28C17BE3DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -119,9 +119,6 @@
     <t>Ismail Mediouna</t>
   </si>
   <si>
-    <t xml:space="preserve">Fares </t>
-  </si>
-  <si>
     <t>Donald Onana</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t>Braddy</t>
+  </si>
+  <si>
+    <t>Fares  Farhi</t>
   </si>
 </sst>
 </file>
@@ -764,7 +764,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1">
         <v>46216</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="1">
         <v>46216</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="1">
         <v>46216</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="1">
         <v>46216</v>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDAE39-36AE-E045-8093-E28C17BE3DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345A1271-96DC-7744-8FDB-A0274B70D3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Sandro Marcon</t>
   </si>
   <si>
-    <t xml:space="preserve">Bradley </t>
-  </si>
-  <si>
     <t>Pharell Cafara</t>
   </si>
   <si>
@@ -125,10 +122,10 @@
     <t>Antoine Leberre</t>
   </si>
   <si>
-    <t>Braddy</t>
-  </si>
-  <si>
     <t>Fares  Farhi</t>
+  </si>
+  <si>
+    <t>Brady Gouandjia</t>
   </si>
 </sst>
 </file>
@@ -723,15 +720,18 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1">
         <v>46216</v>
+      </c>
+      <c r="C20">
+        <v>56.4</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1">
         <v>46216</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1">
         <v>46216</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1">
         <v>46216</v>
@@ -764,7 +764,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" s="1">
         <v>46216</v>
@@ -775,10 +775,13 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="1">
         <v>46216</v>
+      </c>
+      <c r="C25">
+        <v>82.4</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -788,10 +791,13 @@
       <c r="B26" s="1">
         <v>46216</v>
       </c>
+      <c r="C26">
+        <v>65</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1">
         <v>46216</v>
@@ -801,15 +807,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="1">
-        <v>46216</v>
-      </c>
-      <c r="C28">
-        <v>56.4</v>
-      </c>
+      <c r="B28" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345A1271-96DC-7744-8FDB-A0274B70D3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765A7D0B-6141-FE45-A6C7-1DA9430B846B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="5600" yWindow="1720" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>Brady Gouandjia</t>
+  </si>
+  <si>
+    <t>Romain Antunes</t>
+  </si>
+  <si>
+    <t>Kamal Bafounta</t>
   </si>
 </sst>
 </file>
@@ -499,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -720,40 +726,40 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1">
         <v>46216</v>
       </c>
       <c r="C20">
-        <v>56.4</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="1">
         <v>46216</v>
       </c>
       <c r="C21">
-        <v>66.400000000000006</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="1">
         <v>46216</v>
       </c>
       <c r="C22">
-        <v>61.5</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1">
         <v>46216</v>
@@ -764,50 +770,58 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1">
         <v>46216</v>
       </c>
       <c r="C24">
-        <v>67.900000000000006</v>
+        <v>82.4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1">
         <v>46216</v>
       </c>
       <c r="C25">
-        <v>82.4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B26" s="1">
         <v>46216</v>
       </c>
       <c r="C26">
-        <v>65</v>
+        <v>78.099999999999994</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27" s="1">
         <v>46216</v>
       </c>
       <c r="C27">
-        <v>78.099999999999994</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
       <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765A7D0B-6141-FE45-A6C7-1DA9430B846B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13219DD-1FDF-3E40-B24C-D9D9F683DB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5600" yWindow="1720" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="18280" yWindow="680" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>Kamal Bafounta</t>
+  </si>
+  <si>
+    <t>Sofiane</t>
   </si>
 </sst>
 </file>
@@ -505,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -814,13 +817,148 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13219DD-1FDF-3E40-B24C-D9D9F683DB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55290D65-0103-3F4F-A22E-728770EB4036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18280" yWindow="680" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -141,12 +141,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -170,10 +179,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -539,6 +554,9 @@
       <c r="C2">
         <v>79.599999999999994</v>
       </c>
+      <c r="D2" s="3">
+        <v>8.7999999999999995E-2</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -550,6 +568,9 @@
       <c r="C3">
         <v>90.3</v>
       </c>
+      <c r="D3" s="3">
+        <v>0.10299999999999999</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -561,6 +582,9 @@
       <c r="C4">
         <v>81.8</v>
       </c>
+      <c r="D4" s="3">
+        <v>9.8000000000000004E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -572,6 +596,9 @@
       <c r="C5">
         <v>91</v>
       </c>
+      <c r="D5" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -583,6 +610,9 @@
       <c r="C6">
         <v>78</v>
       </c>
+      <c r="D6" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -594,6 +624,9 @@
       <c r="C7">
         <v>78.599999999999994</v>
       </c>
+      <c r="D7" s="3">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -605,6 +638,9 @@
       <c r="C8">
         <v>77.099999999999994</v>
       </c>
+      <c r="D8" s="3">
+        <v>8.7999999999999995E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -616,6 +652,9 @@
       <c r="C9">
         <v>86.9</v>
       </c>
+      <c r="D9" s="3">
+        <v>7.8E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -627,6 +666,9 @@
       <c r="C10">
         <v>76.400000000000006</v>
       </c>
+      <c r="D10" s="3">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -638,6 +680,9 @@
       <c r="C11">
         <v>66.5</v>
       </c>
+      <c r="D11" s="3">
+        <v>4.1000000000000002E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -649,6 +694,9 @@
       <c r="C12">
         <v>81</v>
       </c>
+      <c r="D12" s="3">
+        <v>8.7999999999999995E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -660,6 +708,9 @@
       <c r="C13">
         <v>75</v>
       </c>
+      <c r="D13" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -671,6 +722,9 @@
       <c r="C14">
         <v>64.900000000000006</v>
       </c>
+      <c r="D14" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -682,6 +736,9 @@
       <c r="C15">
         <v>78.2</v>
       </c>
+      <c r="D15" s="3">
+        <v>5.8000000000000003E-2</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -693,8 +750,11 @@
       <c r="C16">
         <v>61.2</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="3">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -704,8 +764,11 @@
       <c r="C17">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="3">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -715,8 +778,11 @@
       <c r="C18">
         <v>69.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="3">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -726,8 +792,11 @@
       <c r="C19">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19" s="3">
+        <v>8.3000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -737,8 +806,11 @@
       <c r="C20">
         <v>66.400000000000006</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20" s="3">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -748,8 +820,11 @@
       <c r="C21">
         <v>61.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21" s="3">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -759,8 +834,11 @@
       <c r="C22">
         <v>67.900000000000006</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -770,8 +848,11 @@
       <c r="C23">
         <v>67.900000000000006</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -781,8 +862,11 @@
       <c r="C24">
         <v>82.4</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -792,8 +876,11 @@
       <c r="C25">
         <v>65</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25" s="3">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -803,8 +890,11 @@
       <c r="C26">
         <v>78.099999999999994</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -814,152 +904,413 @@
       <c r="C27">
         <v>56.4</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27" s="3">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B28" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C28">
+        <v>79.2</v>
+      </c>
+      <c r="D28" s="4">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B29" s="1">
+        <v>46230</v>
+      </c>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B30" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C30">
+        <v>82.6</v>
+      </c>
+      <c r="D30" s="4">
+        <v>8.3000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B31" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C31">
+        <v>90.7</v>
+      </c>
+      <c r="D31" s="4">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B32" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C32">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="D32" s="4">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B33" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C33">
+        <v>79.2</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B34" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C34">
+        <v>76.3</v>
+      </c>
+      <c r="D34" s="4">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B35" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C35">
+        <v>87.5</v>
+      </c>
+      <c r="D35" s="4">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B36" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C36">
+        <v>77.2</v>
+      </c>
+      <c r="D36" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B37" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C37">
+        <v>67</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B38" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C38">
+        <v>81.2</v>
+      </c>
+      <c r="D38" s="4">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B39" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C39">
+        <v>75.7</v>
+      </c>
+      <c r="D39" s="4">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B40" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C40">
+        <v>65.7</v>
+      </c>
+      <c r="D40" s="4">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B41" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C41">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="D41" s="4">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B42" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C42">
+        <v>62.6</v>
+      </c>
+      <c r="D42" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B43" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C43">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="D43" s="4">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B44" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C44">
+        <v>70.8</v>
+      </c>
+      <c r="D44" s="4">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B45" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C45">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="D45" s="4">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B46" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C46">
+        <v>66.8</v>
+      </c>
+      <c r="D46" s="4">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B47" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C47">
+        <v>63.2</v>
+      </c>
+      <c r="D47" s="4">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B48" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C48">
+        <v>68.3</v>
+      </c>
+      <c r="D48" s="4">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B49" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C49">
+        <v>69.8</v>
+      </c>
+      <c r="D49" s="4">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B50" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C50">
+        <v>82.3</v>
+      </c>
+      <c r="D50" s="4">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B51" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C51">
+        <v>66</v>
+      </c>
+      <c r="D51" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B52" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C52">
+        <v>78.5</v>
+      </c>
+      <c r="D52" s="4">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B53" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C53">
+        <v>57</v>
+      </c>
+      <c r="D53" s="4">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C54">
+        <v>72.8</v>
+      </c>
+      <c r="D54" s="4">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B55" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C55">
+        <v>88.4</v>
+      </c>
+      <c r="D55" s="4">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>32</v>
       </c>
+      <c r="B56" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C56">
+        <v>84</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B57" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55290D65-0103-3F4F-A22E-728770EB4036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D936F2-3575-AE45-90C2-4AFE8B53D718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="11560" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -134,7 +134,7 @@
     <t>Kamal Bafounta</t>
   </si>
   <si>
-    <t>Sofiane</t>
+    <t>Sofiane Belkheir</t>
   </si>
 </sst>
 </file>
@@ -186,7 +186,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -523,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -1310,7 +1310,260 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B57" s="1"/>
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C59">
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C65">
+        <v>78.099999999999994</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C66">
+        <v>67.400000000000006</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C70">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C71">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C76">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>28</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>26</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>29</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C83">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>31</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C84">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>32</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46252</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D936F2-3575-AE45-90C2-4AFE8B53D718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04D7C83-F025-7B44-BB77-96592AE7AEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="11560" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="35">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>Sofiane Belkheir</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>Marc</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -1324,6 +1330,9 @@
       <c r="B58" s="1">
         <v>46252</v>
       </c>
+      <c r="C58">
+        <v>93</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
@@ -1343,6 +1352,9 @@
       <c r="B60" s="1">
         <v>46252</v>
       </c>
+      <c r="C60">
+        <v>89.6</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
@@ -1351,6 +1363,9 @@
       <c r="B61" s="1">
         <v>46252</v>
       </c>
+      <c r="C61">
+        <v>76.900000000000006</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
@@ -1359,6 +1374,9 @@
       <c r="B62" s="1">
         <v>46252</v>
       </c>
+      <c r="C62">
+        <v>81.599999999999994</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
@@ -1367,6 +1385,9 @@
       <c r="B63" s="1">
         <v>46252</v>
       </c>
+      <c r="C63">
+        <v>75.400000000000006</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
@@ -1375,6 +1396,9 @@
       <c r="B64" s="1">
         <v>46252</v>
       </c>
+      <c r="C64">
+        <v>87.9</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
@@ -1405,6 +1429,9 @@
       <c r="B67" s="1">
         <v>46252</v>
       </c>
+      <c r="C67">
+        <v>80.5</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
@@ -1413,6 +1440,9 @@
       <c r="B68" s="1">
         <v>46252</v>
       </c>
+      <c r="C68">
+        <v>74</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
@@ -1421,6 +1451,9 @@
       <c r="B69" s="1">
         <v>46252</v>
       </c>
+      <c r="C69">
+        <v>65.8</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
@@ -1451,6 +1484,9 @@
       <c r="B72" s="1">
         <v>46252</v>
       </c>
+      <c r="C72">
+        <v>73.099999999999994</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
@@ -1459,6 +1495,9 @@
       <c r="B73" s="1">
         <v>46252</v>
       </c>
+      <c r="C73">
+        <v>71.099999999999994</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
@@ -1467,6 +1506,9 @@
       <c r="B74" s="1">
         <v>46252</v>
       </c>
+      <c r="C74">
+        <v>77.2</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
@@ -1475,6 +1517,9 @@
       <c r="B75" s="1">
         <v>46252</v>
       </c>
+      <c r="C75">
+        <v>66.400000000000006</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
@@ -1502,6 +1547,9 @@
       <c r="B78" s="1">
         <v>46252</v>
       </c>
+      <c r="C78">
+        <v>69.7</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
@@ -1518,6 +1566,9 @@
       <c r="B80" s="1">
         <v>46252</v>
       </c>
+      <c r="C80">
+        <v>64</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
@@ -1526,6 +1577,9 @@
       <c r="B81" s="1">
         <v>46252</v>
       </c>
+      <c r="C81">
+        <v>79.599999999999994</v>
+      </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
@@ -1563,6 +1617,25 @@
       </c>
       <c r="B85" s="1">
         <v>46252</v>
+      </c>
+      <c r="C85">
+        <v>80.400000000000006</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87">
+        <v>88.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04D7C83-F025-7B44-BB77-96592AE7AEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E69939D-E420-1C49-AA40-48F0B63B809D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="11560" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -137,10 +137,10 @@
     <t>Sofiane Belkheir</t>
   </si>
   <si>
-    <t>Brian</t>
-  </si>
-  <si>
-    <t>Marc</t>
+    <t>Brian Chevreuil</t>
+  </si>
+  <si>
+    <t>Marc Thomas</t>
   </si>
 </sst>
 </file>
@@ -150,7 +150,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -161,6 +161,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -185,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -193,6 +199,12 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1322,6 +1334,7 @@
       <c r="B57" s="1">
         <v>46252</v>
       </c>
+      <c r="D57" s="5"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
@@ -1333,6 +1346,9 @@
       <c r="C58">
         <v>93</v>
       </c>
+      <c r="D58" s="6">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
@@ -1344,6 +1360,9 @@
       <c r="C59">
         <v>83.4</v>
       </c>
+      <c r="D59" s="6">
+        <v>7.8E-2</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
@@ -1355,6 +1374,9 @@
       <c r="C60">
         <v>89.6</v>
       </c>
+      <c r="D60" s="6">
+        <v>7.8E-2</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
@@ -1366,6 +1388,9 @@
       <c r="C61">
         <v>76.900000000000006</v>
       </c>
+      <c r="D61" s="6">
+        <v>6.2E-2</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
@@ -1377,6 +1402,9 @@
       <c r="C62">
         <v>81.599999999999994</v>
       </c>
+      <c r="D62" s="6">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
@@ -1388,6 +1416,9 @@
       <c r="C63">
         <v>75.400000000000006</v>
       </c>
+      <c r="D63" s="6">
+        <v>7.4999999999999997E-2</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
@@ -1399,8 +1430,11 @@
       <c r="C64">
         <v>87.9</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D64" s="6">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -1410,8 +1444,11 @@
       <c r="C65">
         <v>78.099999999999994</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D65" s="6">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -1421,8 +1458,11 @@
       <c r="C66">
         <v>67.400000000000006</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D66" s="6">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -1432,8 +1472,11 @@
       <c r="C67">
         <v>80.5</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D67" s="6">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -1443,8 +1486,11 @@
       <c r="C68">
         <v>74</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D68" s="6">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -1454,8 +1500,11 @@
       <c r="C69">
         <v>65.8</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D69" s="6">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>20</v>
       </c>
@@ -1465,8 +1514,11 @@
       <c r="C70">
         <v>79.2</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D70" s="6">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -1476,8 +1528,11 @@
       <c r="C71">
         <v>64.099999999999994</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D71" s="6">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>22</v>
       </c>
@@ -1487,8 +1542,11 @@
       <c r="C72">
         <v>73.099999999999994</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D72" s="6">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -1498,8 +1556,11 @@
       <c r="C73">
         <v>71.099999999999994</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D73" s="6">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -1509,8 +1570,11 @@
       <c r="C74">
         <v>77.2</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D74" s="6">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>23</v>
       </c>
@@ -1520,8 +1584,11 @@
       <c r="C75">
         <v>66.400000000000006</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D75" s="6">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>24</v>
       </c>
@@ -1531,16 +1598,20 @@
       <c r="C76">
         <v>63.8</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D76" s="6">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>25</v>
       </c>
       <c r="B77" s="1">
         <v>46252</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D77" s="6"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -1550,16 +1621,20 @@
       <c r="C78">
         <v>69.7</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D78" s="6">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>26</v>
       </c>
       <c r="B79" s="1">
         <v>46252</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D79" s="6"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -1569,8 +1644,11 @@
       <c r="C80">
         <v>64</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D80" s="6">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -1580,16 +1658,18 @@
       <c r="C81">
         <v>79.599999999999994</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D81" s="6"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>29</v>
       </c>
       <c r="B82" s="1">
         <v>46252</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D82" s="6"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -1599,8 +1679,11 @@
       <c r="C83">
         <v>73</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D83" s="6">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>31</v>
       </c>
@@ -1610,8 +1693,11 @@
       <c r="C84">
         <v>86.2</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D84" s="6">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>32</v>
       </c>
@@ -1621,21 +1707,30 @@
       <c r="C85">
         <v>80.400000000000006</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D85" s="6">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>33</v>
       </c>
       <c r="C86">
         <v>70.2</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D86" s="6">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>34</v>
       </c>
       <c r="C87">
         <v>88.9</v>
+      </c>
+      <c r="D87" s="6">
+        <v>8.5999999999999993E-2</v>
       </c>
     </row>
   </sheetData>
